--- a/video_plans/shoot_protocols_plan.xlsx
+++ b/video_plans/shoot_protocols_plan.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,12 @@
           <t>3 bottles, plus empty bottles</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="3">
       <c r="A3" s="3" t="inlineStr">
@@ -534,6 +540,12 @@
           <t>4 bottles</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4" customFormat="1" s="3">
       <c r="A4" s="3" t="inlineStr">
@@ -561,6 +573,12 @@
           <t>mg x 10, water</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="3">
       <c r="A5" s="3" t="inlineStr">
@@ -588,6 +606,12 @@
           <t>mg x 10, water</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6" customFormat="1" s="3">
       <c r="A6" s="3" t="inlineStr">
@@ -615,6 +639,12 @@
           <t>mg x 40, water</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7" customFormat="1" s="3">
       <c r="A7" s="3" t="inlineStr">
@@ -642,6 +672,12 @@
           <t>mg x 10, ethanol</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8" customFormat="1" s="3">
       <c r="A8" s="3" t="inlineStr">
@@ -664,6 +700,12 @@
           <t>1 bottle</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9" customFormat="1" s="3">
       <c r="A9" s="3" t="inlineStr">
@@ -691,6 +733,12 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10" customFormat="1" s="3">
       <c r="A10" s="3" t="inlineStr">
@@ -718,6 +766,12 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11" customFormat="1" s="3">
       <c r="A11" s="3" t="inlineStr">
@@ -745,6 +799,12 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12" customFormat="1" s="3">
       <c r="A12" s="4" t="inlineStr">
@@ -773,6 +833,16 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>dropped</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no large plates could be found</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="1" s="3">
       <c r="A13" s="3" t="inlineStr">
@@ -859,6 +929,16 @@
           <t>controls video</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>simplified on the day from what was planned</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="1" s="3">
       <c r="A16" s="3" t="inlineStr">
@@ -888,9 +968,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>controls video</t>
-        </is>
-      </c>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17" customFormat="1" s="2">
       <c r="A17" s="3" t="inlineStr">
@@ -920,9 +1006,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>controls video</t>
-        </is>
-      </c>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18" customFormat="1" s="2">
       <c r="A18" s="4" t="inlineStr">
@@ -952,9 +1044,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>controls video</t>
-        </is>
-      </c>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -984,7 +1082,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>controls video</t>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>same procedure as 2a; the plating was done, just not filmed</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1119,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1161,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -1259,6 +1387,16 @@
           <t>assembles_into</t>
         </is>
       </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>filmed</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="1" s="3">
       <c r="A2" s="3" t="inlineStr">
@@ -1281,6 +1419,12 @@
           <t>3 bottles, plus empty bottles</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1303,6 +1447,12 @@
           <t>4 bottles</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4" customFormat="1" s="3">
       <c r="A4" s="3" t="inlineStr">
@@ -1330,6 +1480,12 @@
           <t>mg x 10, water</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="3">
       <c r="A5" s="3" t="inlineStr">
@@ -1357,6 +1513,12 @@
           <t>mg x 10, water</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6" customFormat="1" s="3">
       <c r="A6" s="3" t="inlineStr">
@@ -1384,6 +1546,12 @@
           <t>mg x 40, water</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7" customFormat="1" s="3">
       <c r="A7" s="3" t="inlineStr">
@@ -1411,6 +1579,12 @@
           <t>mg x 10, ethanol</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8" customFormat="1" s="3">
       <c r="A8" s="3" t="inlineStr">
@@ -1433,6 +1607,12 @@
           <t>1 bottle</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9" customFormat="1" s="3">
       <c r="A9" s="3" t="inlineStr">
@@ -1460,6 +1640,12 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10" customFormat="1" s="3">
       <c r="A10" s="3" t="inlineStr">
@@ -1487,6 +1673,12 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11" customFormat="1" s="3">
       <c r="A11" s="3" t="inlineStr">
@@ -1514,6 +1706,12 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12" customFormat="1" s="3">
       <c r="A12" s="4" t="inlineStr">
@@ -1542,6 +1740,16 @@
           <t>plate pouring video</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>dropped</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no large plates could be found</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="1" s="3">
       <c r="A13" s="3" t="inlineStr">
@@ -1628,6 +1836,16 @@
           <t>controls video</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>simplified on the day from what was planned</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="1" s="3">
       <c r="A16" s="3" t="inlineStr">
@@ -1657,9 +1875,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>controls video</t>
-        </is>
-      </c>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17" customFormat="1" s="3">
       <c r="A17" s="3" t="inlineStr">
@@ -1689,9 +1913,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>controls video</t>
-        </is>
-      </c>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18" customFormat="1" s="3">
       <c r="A18" s="4" t="inlineStr">
@@ -1721,9 +1951,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>controls video</t>
-        </is>
-      </c>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19" customFormat="1" s="2">
       <c r="A19" s="4" t="inlineStr">
@@ -1753,7 +1989,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>controls video</t>
+          <t>minipreps into cells</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>same procedure as 2a; the plating was done, just not filmed</t>
         </is>
       </c>
     </row>
@@ -1885,7 +2131,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
         </is>
       </c>
     </row>
@@ -1917,7 +2173,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
         </is>
       </c>
     </row>

--- a/video_plans/shoot_protocols_plan.xlsx
+++ b/video_plans/shoot_protocols_plan.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -492,22 +492,22 @@
       </c>
     </row>
     <row r="2" customFormat="1" s="3">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>agar_fresh</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Preparation of LB Agar (250 mL bottles)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>3 bottles, plus empty bottles</t>
         </is>
@@ -517,25 +517,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>broth_2yt</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Preparation of 2YT Broth (250 mL bottles)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>4 bottles</t>
         </is>
@@ -545,30 +544,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4" customFormat="1" s="3">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>abx_carb</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>100 mg/mL</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>mg x 10, water</t>
         </is>
@@ -578,30 +576,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="3">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>abx_spec</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>100 mg/mL</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>mg x 10, water</t>
         </is>
@@ -611,30 +608,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6" customFormat="1" s="3">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>abx_kan</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>25 mg/mL</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>mg x 40, water</t>
         </is>
@@ -644,30 +640,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7" customFormat="1" s="3">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>abx_erm</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>100 mg/mL</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>mg x 10, ethanol</t>
         </is>
@@ -677,25 +672,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8" customFormat="1" s="3">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>agar_remelt</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Re-melting Solidified LB Agar</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>1 bottle</t>
         </is>
@@ -705,25 +699,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9" customFormat="1" s="3">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>pour_many_plates</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Pouring many Carb petri dishes</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Carb, 1 stack</t>
         </is>
@@ -738,25 +731,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10" customFormat="1" s="3">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>pour_few_plates1</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Pouring a few Erm petri dishes with conicol</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Erm, 3 plates</t>
         </is>
@@ -771,25 +763,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11" customFormat="1" s="3">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>pour_few_plates2</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Pouring a few spec petri dishes with bottle</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Spec, 4 plates</t>
         </is>
@@ -804,25 +795,23 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12" customFormat="1" s="3">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>pour_large_plate</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Pouring and Spreading Large Petri Dishes (150 mm)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>150 mm plates; existing module</t>
@@ -845,22 +834,22 @@
       </c>
     </row>
     <row r="13" customFormat="1" s="3">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>(no vid)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Pouring a few kan petri dishes</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Kan, 3 plates</t>
         </is>
@@ -872,22 +861,22 @@
       </c>
     </row>
     <row r="14" customFormat="1" s="3">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>(no vid)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Pouring a few plain petri dishes</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>no ab, 3 plates</t>
         </is>
@@ -899,27 +888,27 @@
       </c>
     </row>
     <row r="15" customFormat="1" s="3">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ctrl_streak</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Streaking control strain</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>vid 1: 3 plates do all 4</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>neg, streak, and put carb one on spec, streak and neg for others</t>
         </is>
@@ -941,27 +930,27 @@
       </c>
     </row>
     <row r="16" customFormat="1" s="3">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ctrl_transform1</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Label plates, thaw cells, incubate dna</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>4 reactions</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>each control plasmid (carb, kan, spec, erm) — same for all four; the fork is at step 2</t>
         </is>
@@ -976,30 +965,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17" customFormat="1" s="2">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>ctrl_transform2a</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Heat shock and plate</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>1 reaction</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>carb only — no rescue, plate straight away</t>
         </is>
@@ -1014,30 +1002,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18" customFormat="1" s="2">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>ctrl_transform2b</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Heat shock and rescue</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>3 reactions</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>kan, spec, erm — 200 uL 2YT, 37 C, 1 h; do not plate yet</t>
         </is>
@@ -1052,30 +1039,29 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>ctrl_transform3a</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Plate from a rescue</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>3 reactions</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>kan, spec, erm — plate all the liquid; dry before inverting</t>
         </is>
@@ -1097,22 +1083,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>bestP_transform1</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Label plates, thaw cells, incubate dna</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>7 reactions, on carb</t>
         </is>
@@ -1134,22 +1120,22 @@
       </c>
     </row>
     <row r="21" customFormat="1" s="3">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>bestP_transform2a</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Heat shock and plate</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>7 reactions, on carb</t>
         </is>
@@ -1184,90 +1170,115 @@
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>lab_tour</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lab tour</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>one continuous walking shot</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>room must be quiet; say every location out loud</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>safety video</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>biosafety</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lab rules and biosafety</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>static, at a bench</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>the six must-say lines map onto quiz questions</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>safety video</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>parafilm</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Sealing Petri Dishes with Parafilm</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="1" s="2">
+      <c r="A27" t="inlineStr">
         <is>
           <t>ctrl_read</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Examine and photograph plates</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>controls video</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>bestp_pick</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Pick bestP's colonies into a block</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Full block</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>BestP video</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" customFormat="1" s="2">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>pp6_pick</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Pick pp6 clones into a 15mL conicol</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>pp6</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>do 2</t>
         </is>
       </c>
     </row>
@@ -1275,29 +1286,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Day 3</t>
+          <t>Later — plates held in the fridge</t>
         </is>
       </c>
     </row>
     <row r="30" customFormat="1" s="2">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>bestp_tecan</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Tecan the bestp's from a block</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bestp_pick</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pick bestP's colonies into a block</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>56 wells</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Full block</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1306,31 +1317,87 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pp6_pick</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pick pp6 clones into a 15mL conicol</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>pp6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>do 2</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bestp_tecan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tecan the bestp's from a block</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bestp</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>56 wells</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BestP video</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Whenever</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>bestp_intro</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>
@@ -1347,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -1424,7 +1491,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3" customFormat="1" s="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1452,7 +1518,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4" customFormat="1" s="3">
       <c r="A4" s="3" t="inlineStr">
@@ -1485,7 +1550,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="3">
       <c r="A5" s="3" t="inlineStr">
@@ -1518,7 +1582,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6" customFormat="1" s="3">
       <c r="A6" s="3" t="inlineStr">
@@ -1551,7 +1614,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7" customFormat="1" s="3">
       <c r="A7" s="3" t="inlineStr">
@@ -1584,7 +1646,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8" customFormat="1" s="3">
       <c r="A8" s="3" t="inlineStr">
@@ -1612,7 +1673,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9" customFormat="1" s="3">
       <c r="A9" s="3" t="inlineStr">
@@ -1645,7 +1705,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10" customFormat="1" s="3">
       <c r="A10" s="3" t="inlineStr">
@@ -1678,7 +1737,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11" customFormat="1" s="3">
       <c r="A11" s="3" t="inlineStr">
@@ -1711,7 +1769,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12" customFormat="1" s="3">
       <c r="A12" s="4" t="inlineStr">
@@ -1883,7 +1940,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17" customFormat="1" s="3">
       <c r="A17" s="3" t="inlineStr">
@@ -1921,7 +1977,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18" customFormat="1" s="3">
       <c r="A18" s="4" t="inlineStr">
@@ -1959,7 +2014,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19" customFormat="1" s="2">
       <c r="A19" s="4" t="inlineStr">
@@ -2004,97 +2058,127 @@
       </c>
     </row>
     <row r="20" customFormat="1" s="2">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>lab_tour</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Lab tour</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>one continuous walking shot</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>room must be quiet; say every location out loud</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>safety video</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="1" s="2">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>biosafety</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Lab rules and biosafety</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>static, at a bench</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>the six must-say lines map onto quiz questions</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>safety video</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="1" s="2">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>parafilm</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Sealing Petri Dishes with Parafilm</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="1" s="2">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="1" s="2">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>ctrl_read</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Examine and photograph plates</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>controls video</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" customFormat="1" s="2">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>bestp_intro</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>BestP video</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="1" s="2">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>(agar_fresh)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Preparation of LB Agar (250 mL bottles)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="1" s="2">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>(pour_many_plates)</t>
+          <t>bestp_intro</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Pouring Standard Petri Dishes</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2111,12 +2195,12 @@
     <row r="25" customFormat="1" s="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>bestP_transform1</t>
+          <t>(agar_fresh)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Label plates, thaw cells, incubate dna</t>
+          <t>Preparation of LB Agar (250 mL bottles)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2124,36 +2208,21 @@
           <t>bestp</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>7 reactions, on carb</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="26" customFormat="1" s="2">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>bestP_transform2a</t>
+          <t>(pour_many_plates)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Heat shock and plate</t>
+          <t>Pouring Standard Petri Dishes</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2161,41 +2230,21 @@
           <t>bestp</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>7 reactions, on carb</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>carb — no rescue</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>bestp_pick</t>
+          <t>bestP_transform1</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Pick bestP's colonies into a block</t>
+          <t>Label plates, thaw cells, incubate dna</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2205,59 +2254,138 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Full block</t>
+          <t>7 reactions, on carb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>pp6_pick</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Pick pp6 clones into a 15mL conicol</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>pp6</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>do 2</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>bestP_transform2a</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Heat shock and plate</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>bestp</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7 reactions, on carb</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>carb — no rescue</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>bestp_pick</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Pick bestP's colonies into a block</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>bestp</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Full block</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BestP video</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>pp6_pick</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Pick pp6 clones into a 15mL conicol</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>pp6</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>do 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>bestp_tecan</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Tecan the bestp's from a block</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>56 wells</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>

--- a/video_plans/shoot_protocols_plan.xlsx
+++ b/video_plans/shoot_protocols_plan.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lab tour</t>
+          <t>Lab tour and biosafety</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>room must be quiet; say every location out loud</t>
+          <t>every rule made at the object it belongs to, not batched at a bench</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1209,49 +1209,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>biosafety</t>
+          <t>parafilm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lab rules and biosafety</t>
+          <t>Sealing Petri Dishes with Parafilm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>safety</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>static, at a bench</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>the six must-say lines map onto quiz questions</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>safety video</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>pending</t>
+          <t>general</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>parafilm</t>
+          <t>ctrl_read</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sealing Petri Dishes with Parafilm</t>
+          <t>Examine and photograph plates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1259,145 +1239,128 @@
           <t>general</t>
         </is>
       </c>
-    </row>
-    <row r="27" customFormat="1" s="2">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ctrl_read</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Examine and photograph plates</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>controls video</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
+    <row r="27" customFormat="1" s="2"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Later — plates held in the fridge</t>
+          <t>bestp_pick</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pick bestP's colonies into a block</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bestp</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Full block</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="30" customFormat="1" s="2">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bestp_pick</t>
+          <t>pp6_pick</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pick bestP's colonies into a block</t>
+          <t>Pick pp6 clones into a 15mL conicol</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bestp</t>
+          <t>pp6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Full block</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>BestP video</t>
+          <t>do 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pp6_pick</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Pick pp6 clones into a 15mL conicol</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>pp6</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>do 2</t>
+          <t>Day 4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Day 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
           <t>bestp_tecan</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Tecan the bestp's from a block</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>56 wells</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Whenever</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Whenever</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
           <t>bestp_intro</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>
@@ -1414,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -1449,39 +1412,39 @@
           <t>notes</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>assembles_into</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>filmed</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>outcome</t>
         </is>
       </c>
     </row>
     <row r="2" customFormat="1" s="3">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>agar_fresh</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Preparation of LB Agar (250 mL bottles)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>3 bottles, plus empty bottles</t>
         </is>
@@ -1493,22 +1456,22 @@
       </c>
     </row>
     <row r="3" customFormat="1" s="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>broth_2yt</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Preparation of 2YT Broth (250 mL bottles)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>4 bottles</t>
         </is>
@@ -1520,27 +1483,27 @@
       </c>
     </row>
     <row r="4" customFormat="1" s="3">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>abx_carb</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>100 mg/mL</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>mg x 10, water</t>
         </is>
@@ -1552,27 +1515,27 @@
       </c>
     </row>
     <row r="5" customFormat="1" s="3">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>abx_spec</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>100 mg/mL</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>mg x 10, water</t>
         </is>
@@ -1584,27 +1547,27 @@
       </c>
     </row>
     <row r="6" customFormat="1" s="3">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>abx_kan</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>25 mg/mL</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>mg x 40, water</t>
         </is>
@@ -1616,27 +1579,27 @@
       </c>
     </row>
     <row r="7" customFormat="1" s="3">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>abx_erm</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Preparation of Antibiotic 1000x Stock</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>100 mg/mL</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>mg x 10, ethanol</t>
         </is>
@@ -1648,22 +1611,22 @@
       </c>
     </row>
     <row r="8" customFormat="1" s="3">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>agar_remelt</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Re-melting Solidified LB Agar</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>1 bottle</t>
         </is>
@@ -1675,22 +1638,22 @@
       </c>
     </row>
     <row r="9" customFormat="1" s="3">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>pour_many_plates</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Pouring many Carb petri dishes</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Carb, 1 stack</t>
         </is>
@@ -1707,22 +1670,22 @@
       </c>
     </row>
     <row r="10" customFormat="1" s="3">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>pour_few_plates1</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Pouring a few Erm petri dishes with conicol</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Erm, 3 plates</t>
         </is>
@@ -1739,22 +1702,22 @@
       </c>
     </row>
     <row r="11" customFormat="1" s="3">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>pour_few_plates2</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Pouring a few spec petri dishes with bottle</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Spec, 4 plates</t>
         </is>
@@ -1771,22 +1734,21 @@
       </c>
     </row>
     <row r="12" customFormat="1" s="3">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>pour_large_plate</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Pouring and Spreading Large Petri Dishes (150 mm)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>150 mm plates; existing module</t>
@@ -1809,22 +1771,22 @@
       </c>
     </row>
     <row r="13" customFormat="1" s="3">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>(no vid)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Pouring a few kan petri dishes</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Kan, 3 plates</t>
         </is>
@@ -1836,22 +1798,22 @@
       </c>
     </row>
     <row r="14" customFormat="1" s="3">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>(no vid)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Pouring a few plain petri dishes</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>no ab, 3 plates</t>
         </is>
@@ -1863,27 +1825,27 @@
       </c>
     </row>
     <row r="15" customFormat="1" s="3">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ctrl_streak</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Streaking control strain</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>vid 1: 3 plates do all 4</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>neg, streak, and put carb one on spec, streak and neg for others</t>
         </is>
@@ -1905,27 +1867,27 @@
       </c>
     </row>
     <row r="16" customFormat="1" s="3">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ctrl_transform1</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Label plates, thaw cells, incubate dna</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>4 reactions</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>each control plasmid (carb, kan, spec, erm) — same for all four; the fork is at step 2</t>
         </is>
@@ -1942,27 +1904,27 @@
       </c>
     </row>
     <row r="17" customFormat="1" s="3">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>ctrl_transform2a</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Heat shock and plate</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>1 reaction</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>carb only — no rescue, plate straight away</t>
         </is>
@@ -1979,27 +1941,27 @@
       </c>
     </row>
     <row r="18" customFormat="1" s="3">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>ctrl_transform2b</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Heat shock and rescue</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>3 reactions</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>kan, spec, erm — 200 uL 2YT, 37 C, 1 h; do not plate yet</t>
         </is>
@@ -2016,27 +1978,27 @@
       </c>
     </row>
     <row r="19" customFormat="1" s="2">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>ctrl_transform3a</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Plate from a rescue</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>3 reactions</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>kan, spec, erm — plate all the liquid; dry before inverting</t>
         </is>
@@ -2058,29 +2020,29 @@
       </c>
     </row>
     <row r="20" customFormat="1" s="2">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>lab_tour</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Lab tour</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lab tour and biosafety</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>safety</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>one continuous walking shot</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>room must be quiet; say every location out loud</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>every rule made at the object it belongs to, not batched at a bench</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2095,93 +2057,78 @@
       </c>
     </row>
     <row r="21" customFormat="1" s="2">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>biosafety</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Lab rules and biosafety</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>safety</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>static, at a bench</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>the six must-say lines map onto quiz questions</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>safety video</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>parafilm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sealing Petri Dishes with Parafilm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>
     <row r="22" customFormat="1" s="2">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>parafilm</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sealing Petri Dishes with Parafilm</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ctrl_read</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Examine and photograph plates</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>controls video</t>
         </is>
       </c>
     </row>
     <row r="23" customFormat="1" s="2">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>ctrl_read</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Examine and photograph plates</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>general</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bestp_intro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>bestp</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>controls video</t>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="1" s="2">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>bestp_intro</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>(agar_fresh)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Preparation of LB Agar (250 mL bottles)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
@@ -2193,17 +2140,17 @@
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>(agar_fresh)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Preparation of LB Agar (250 mL bottles)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(pour_many_plates)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pouring Standard Petri Dishes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
@@ -2215,177 +2162,155 @@
       </c>
     </row>
     <row r="26" customFormat="1" s="2">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>(pour_many_plates)</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Pouring Standard Petri Dishes</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bestP_transform1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Label plates, thaw cells, incubate dna</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7 reactions, on carb</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bestP_transform2a</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Heat shock and plate</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bestp</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7 reactions, on carb</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>carb — no rescue</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bestp_pick</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pick bestP's colonies into a block</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bestp</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Full block</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>BestP video</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>bestP_transform1</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Label plates, thaw cells, incubate dna</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pp6_pick</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pick pp6 clones into a 15mL conicol</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pp6</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>do 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bestp_tecan</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tecan the bestp's from a block</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>7 reactions, on carb</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>bestP_transform2a</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Heat shock and plate</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>7 reactions, on carb</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>carb — no rescue</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>bestp_pick</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Pick bestP's colonies into a block</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Full block</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>BestP video</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>pp6_pick</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Pick pp6 clones into a 15mL conicol</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>pp6</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>do 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>bestp_tecan</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Tecan the bestp's from a block</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>56 wells</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>

--- a/video_plans/shoot_protocols_plan.xlsx
+++ b/video_plans/shoot_protocols_plan.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -1209,158 +1209,201 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>parafilm</t>
+          <t>ctrl_intro</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sealing Petri Dishes with Parafilm</t>
+          <t>What control strains are and why we keep them</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>general</t>
-        </is>
-      </c>
+          <t>controls</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>no bench work</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>intro to the controls thread; sets up the streak and transformation clips</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>controls video</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>parafilm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sealing Petri Dishes with Parafilm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>store in the Culture Fridge (4 °C), not the Main/Cell-Free fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="1" s="2">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>ctrl_read</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Examine and photograph plates</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>controls video</t>
         </is>
       </c>
     </row>
-    <row r="27" customFormat="1" s="2"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Day 3</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bestp_pick</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Pick bestP's colonies into a block</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>bestp</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Full block</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>BestP video</t>
+          <t>Day 3</t>
         </is>
       </c>
     </row>
     <row r="30" customFormat="1" s="2">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pp6_pick</t>
+          <t>bestp_pick</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pick pp6 clones into a 15mL conicol</t>
+          <t>Pick bestP's colonies into a block</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pp6</t>
+          <t>bestp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>do 2</t>
+          <t>Full block</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Day 4</t>
+          <t>pp6_pick</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pick pp6 clones into a 15mL conicol</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>pp6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>do 2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>bestp_tecan</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Tecan the bestp's from a block</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>56 wells</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Whenever</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Whenever</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>bestp_intro</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>
@@ -1377,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -2059,29 +2102,50 @@
     <row r="21" customFormat="1" s="2">
       <c r="A21" t="inlineStr">
         <is>
-          <t>parafilm</t>
+          <t>ctrl_intro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sealing Petri Dishes with Parafilm</t>
+          <t>What control strains are and why we keep them</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>general</t>
-        </is>
-      </c>
+          <t>controls</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no bench work</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>intro to the controls thread; sets up the streak and transformation clips</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>controls video</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22" customFormat="1" s="2">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ctrl_read</t>
+          <t>parafilm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Examine and photograph plates</t>
+          <t>Sealing Petri Dishes with Parafilm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2089,43 +2153,43 @@
           <t>general</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>controls video</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>store in the Culture Fridge (4 °C), not the Main/Cell-Free fridge</t>
         </is>
       </c>
     </row>
     <row r="23" customFormat="1" s="2">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bestp_intro</t>
+          <t>ctrl_read</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>Examine and photograph plates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bestp</t>
+          <t>general</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>controls video</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="1" s="2">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(agar_fresh)</t>
+          <t>bestp_intro</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Preparation of LB Agar (250 mL bottles)</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2142,12 +2206,12 @@
     <row r="25" customFormat="1" s="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(pour_many_plates)</t>
+          <t>(agar_fresh)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pouring Standard Petri Dishes</t>
+          <t>Preparation of LB Agar (250 mL bottles)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2164,12 +2228,12 @@
     <row r="26" customFormat="1" s="2">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bestP_transform1</t>
+          <t>(pour_many_plates)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Label plates, thaw cells, incubate dna</t>
+          <t>Pouring Standard Petri Dishes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2177,36 +2241,21 @@
           <t>bestp</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7 reactions, on carb</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bestP_transform2a</t>
+          <t>bestP_transform1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Heat shock and plate</t>
+          <t>Label plates, thaw cells, incubate dna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2219,11 +2268,6 @@
           <t>7 reactions, on carb</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>carb — no rescue</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>not filmed — BestP reuses the minipreps-into-cells video</t>
@@ -2236,19 +2280,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
+          <t>covered by ctrl_transform1 — pJ01/pJ12/pJ19 were transformed there</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bestp_pick</t>
+          <t>bestP_transform2a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pick bestP's colonies into a block</t>
+          <t>Heat shock and plate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2258,59 +2302,101 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Full block</t>
+          <t>7 reactions, on carb</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>carb — no rescue</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BestP video</t>
+          <t>not filmed — BestP reuses the minipreps-into-cells video</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>covered by ctrl_transform2a/2b; three references explain BestP without repeating the whole run</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pp6_pick</t>
+          <t>bestp_pick</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pick pp6 clones into a 15mL conicol</t>
+          <t>Pick bestP's colonies into a block</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pp6</t>
+          <t>bestp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>do 2</t>
+          <t>Full block</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BestP video</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>pp6_pick</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pick pp6 clones into a 15mL conicol</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pp6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>do 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>bestp_tecan</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Tecan the bestp's from a block</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>bestp</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>56 wells</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>BestP video</t>
         </is>
